--- a/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T13:29:16+00:00</t>
+    <t>2026-08-18T08:27:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-18T08:27:41+00:00</t>
+    <t>2026-08-19T09:48:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T09:48:17+00:00</t>
+    <t>2026-08-19T13:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-19T13:44:28+00:00</t>
+    <t>2026-08-20T07:23:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T07:23:52+00:00</t>
+    <t>2026-08-20T09:16:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T09:16:14+00:00</t>
+    <t>2026-08-20T10:23:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
+++ b/ig/DM-AOUT-2026/CodeSystem-terminologie-lahn.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T10:23:09+00:00</t>
+    <t>2026-08-21T07:25:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
